--- a/accton/dist/20261028_智邦個股模型_v0.3.xlsx
+++ b/accton/dist/20261028_智邦個股模型_v0.3.xlsx
@@ -158,6 +158,7 @@
     <definedName function="false" hidden="false" name="RLO_27" vbProcedure="false">In!$D$37</definedName>
     <definedName function="false" hidden="false" name="RLO_28" vbProcedure="false">In!$D$38</definedName>
     <definedName function="false" hidden="false" name="RLO_29" vbProcedure="false">In!$D$39</definedName>
+    <definedName function="false" hidden="false" name="rm_factor" vbProcedure="false">Val!$B$160</definedName>
     <definedName function="false" hidden="false" name="sh_g" vbProcedure="false">In!$E$69</definedName>
     <definedName function="false" hidden="false" name="sh_g27" vbProcedure="false">In!$E$68</definedName>
     <definedName function="false" hidden="false" name="sh_g27_hi" vbProcedure="false">In!$F$68</definedName>
@@ -174,6 +175,7 @@
     <definedName function="false" hidden="false" name="tf" vbProcedure="false">In!$E$44</definedName>
     <definedName function="false" hidden="false" name="tf_hi" vbProcedure="false">In!$F$44</definedName>
     <definedName function="false" hidden="false" name="tf_lo" vbProcedure="false">In!$D$44</definedName>
+    <definedName function="false" hidden="false" name="tp_comp_adj" vbProcedure="false">Val!$B$161</definedName>
     <definedName function="false" hidden="false" name="tp_g" vbProcedure="false">In!$E$87</definedName>
     <definedName function="false" hidden="false" name="tp_gd" vbProcedure="false">In!$E$88</definedName>
     <definedName function="false" hidden="false" name="tp_r" vbProcedure="false">In!$E$86</definedName>
@@ -223,7 +225,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3056" uniqueCount="823">
   <si>
     <r>
       <rPr>
@@ -3146,26 +3148,512 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NT$2,275</t>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">三情境分歧大：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">A 169.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FactSet </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">170.57 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相近）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">B 133.8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.9%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C 95.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">43.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），差距來自 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CY2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">起的顆數情境；單一變數中白牌份額流失（相對值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.80</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS −18.2%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">交換器市場 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×0.8 −13.8%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Trainium </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">份額流失 −</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10.4%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：追蹤 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">財報與法說（去年在 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11-07</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，約 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上旬）與 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月營收（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11-10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前）：本版 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3Q </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毛利率與費用為假設，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">網路應用產品占比 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">50% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">為 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Assumed</t>
     </r>
     <r>
       <rPr>
@@ -3184,7 +3672,370 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DCF 2,584</t>
+      <t xml:space="preserve">42%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">58% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">時 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FY2028 EPS +6.3%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">／−</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6.7%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。網通 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目前只有一條路徑、三情境相同，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.6T </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">換代的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CPO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">份額風險待 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">markets/network </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改版。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">：加權目標價中的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">改用相對倍數調整後的值（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">第 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">節：同業前瞻倍數中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的倍數比，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">前瞻倍數；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">「照建議做」、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10-29 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料取回）。「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）」維持不調整。重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的第一句已改為公式；重點觀察 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -3203,1178 +4054,35 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Comparable 1,966 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各半），比現價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,775</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-10-22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">28.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，級距 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">25%–50%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單獨為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+10.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。主因是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">不是 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：本模型 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">個月後前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 138.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">比共識前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">EPS 162.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">低 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，在同業前瞻 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">P/E </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">14.2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍下 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Comparable </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">只高一成；</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">DCF </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">單獨 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+45.6%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，因 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ROE 44.8% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">遠高於折現率 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（可發放比例 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">91%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），而現價只有 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2027 EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12.0 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍。共識目標價 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3,500 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">隱含 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">21.6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">倍，比同業高 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">52.0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">三情境分歧大：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">A 169.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FactSet </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">中位數 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">170.57 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">相近）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">B 133.8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20.9%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">C 95.7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">43.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">），差距來自 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CY2028 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">起的顆數情境；單一變數中白牌份額流失（相對值 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.80</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0.70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS −18.2%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">交換器市場 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×0.8 −13.8%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Trainium </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">份額流失 −</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10.4%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">重點觀察 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">：追蹤 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">財報與法說（去年在 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11-07</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，約 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026-11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上旬）與 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月營收（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11-10 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">前）：本版 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3Q </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毛利率與費用為假設，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2026 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">網路應用產品占比 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">50% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">為 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Assumed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">42%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">58% </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">FY2028 EPS +6.3%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">／−</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6.7%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。網通 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">目前只有一條路徑、三情境相同，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.6T </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">換代的 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CPO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">份額風險待 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">markets/network </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">改版。</t>
+      <t xml:space="preserve">3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">與其他說明中的目標價與上檔空間數字為調整前撰寫，以 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Val </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">頁為準。</t>
     </r>
   </si>
   <si>
@@ -27470,6 +27178,1123 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">分位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0.5 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">相對倍數調整（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標倍數＝同業中位數 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年相對同業的 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比；</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Andy 2026-10-27 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">新增，放在本頁最後以免位移既有儲存格）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2017–2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各年度窗口（前一年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月～當年 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月底前瞻 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">P/E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）的中位數（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/data/fwd_mult_hist.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">），</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Verified] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">來源、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Derived] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">彙總；有效值 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 &lt; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">值 ≤ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，無效值以「剔除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」文字列示、不進中位數。本公司或同業有效年數 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">不納入；有效同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">&lt; 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">家或本公司不足時係數＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公司</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016/11–2017/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017/11–2018/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018/11–2019/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019/11–2020/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020/11–2021/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021/11–2022/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022/11–2023/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023/11–2024/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024/11–2025/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/11–2026/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效年數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">納入值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">智邦</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2345.TW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本公司</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2345 TT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">同業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg ANET US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg CLS US Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 6669 TT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomberg 2382 TT Equity BEST_PE_RATIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝未來 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">個月，月底）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數（納入值）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空白＝本公司有效年數不足</t>
+  </si>
+  <si>
+    <t xml:space="preserve">納入的同業家數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年中位數的中位數</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原始比值（本公司 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同業）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝本公司長期比同業便宜（折價），＞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝長期溢價</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值下限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">避免單一歷史異常主導；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_LO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">夾值上限</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">[Assumed] tools/relative_multiple.py </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">的 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">RM_HI</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">相對倍數調整係數</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">資料不足時＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（不調整）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Cambria"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（相對倍數調整後）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">＝</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Comparable </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">目標價（市場主流同業法）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">調整係數；加權目標價使用本列</t>
     </r>
   </si>
   <si>
@@ -32416,7 +33241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.00%"/>
@@ -32429,6 +33254,7 @@
     <numFmt numFmtId="173" formatCode="0.0"/>
     <numFmt numFmtId="174" formatCode="0%"/>
     <numFmt numFmtId="175" formatCode="@"/>
+    <numFmt numFmtId="176" formatCode="0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -32551,7 +33377,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -32689,6 +33515,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -32944,7 +33774,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="170"/>
@@ -33037,21 +33867,27 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="str">
         <f aca="false">"投資建議："&amp;Val!B52&amp;"（依上檔空間固定規則）"</f>
-        <v>投資建議：買進（依上檔空間固定規則）</v>
+        <v>投資建議：強力買進（依上檔空間固定規則）</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
-        <v>15</v>
+      <c r="A20" s="0" t="str">
+        <f aca="false">"重點觀察 1：目標價 NT$"&amp;TEXT(Val!$B$39,"#,##0")&amp;"（DCF "&amp;TEXT(Val!$B$23,"#,##0")&amp;"、Comparable（相對倍數調整後）"&amp;TEXT(tp_comp_adj,"#,##0")&amp;"；DCF 權重 "&amp;TEXT(tp_w_dcf,"0%")&amp;"），比現價 "&amp;TEXT(px,"#,##0")&amp;"（2026-10-22）"&amp;IF(Val!$B$42&gt;=0,"高 "&amp;TEXT(Val!$B$42,"0.0%"),"低 "&amp;TEXT(-Val!$B$42,"0.0%"))&amp;"，級距 "&amp;Val!$B$51&amp;"、投資建議 "&amp;Val!$B$52&amp;"。相對倍數調整係數 "&amp;TEXT(rm_factor,"0.00")&amp;"（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 "&amp;TEXT((tp_w_dcf*Val!$B$23+(1-tp_w_dcf)*Val!$B$35)/px-1,"+0.0%;−0.0%")&amp;"；Comparable 單獨（市場主流同業法、未調整）為 "&amp;TEXT(Val!$B$43,"+0.0%;−0.0%")&amp;"。"&amp;"以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是 DCF 不是 EPS：本模型 12 個月後前瞻 EPS 138.6 比共識前瞻 EPS 162.3 低 14.6%，在同業前瞻 P/E 中位數 14.2 倍下 Comparable 只高一成；DCF 單獨 +45.6%，因 ROE 44.8% 遠高於折現率 10%（可發放比例 91%），而現價只有 FY2027 EP"&amp;"S 的 12.0 倍。共識目標價 3,500 隱含 21.6 倍，比同業高 52.0%。"</f>
+        <v>重點觀察 1：目標價 NT$2,772（DCF 2,584、Comparable（相對倍數調整後）2,961；DCF 權重 50%），比現價 1,775（2026-10-22）高 56.2%，級距 大於 50%、投資建議 強力買進。相對倍數調整係數 1.51（本公司 10 年前瞻倍數中位數 ÷ 同業的中位數，夾在 0.5–2.0；Val 第 0.5 節），調整前加權上檔空間 +28.2%；Comparable 單獨（市場主流同業法、未調整）為 +10.8%。以下為 2026-10-29 相對倍數調整前撰寫的說明，其中數字為調整前：主因是 DCF 不是 EPS：本模型 12 個月後前瞻 EPS 138.6 比共識前瞻 EPS 162.3 低 14.6%，在同業前瞻 P/E 中位數 14.2 倍下 Comparable 只高一成；DCF 單獨 +45.6%，因 ROE 44.8% 遠高於折現率 10%（可發放比例 91%），而現價只有 FY2027 EPS 的 12.0 倍。共識目標價 3,500 隱含 21.6 倍，比同業高 52.0%。</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>17</v>
       </c>
     </row>
@@ -41059,7 +41895,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H140"/>
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -41632,8 +42468,8 @@
         <v>512</v>
       </c>
       <c r="B39" s="25" t="n">
-        <f aca="false">tp_w_dcf*B23+(1-tp_w_dcf)*B35</f>
-        <v>2275.03974290026</v>
+        <f aca="false">tp_w_dcf*B23+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>2772.28652343754</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -41669,7 +42505,7 @@
       </c>
       <c r="B42" s="18" t="n">
         <f aca="false">B39/px-1</f>
-        <v>0.281712531211416</v>
+        <v>0.56185156250002</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41793,7 +42629,7 @@
       </c>
       <c r="B51" s="31" t="str">
         <f aca="false">IF(B42&gt;0.5,"大於 50%",IF(B42&gt;0.25,"25%–50%",IF(B42&gt;=0,"0%–25%",IF(B42&gt;=-0.25,"0%～−25%",IF(B42&gt;=-0.5,"−25%～−50%","小於 −50%")))))</f>
-        <v>25%–50%</v>
+        <v>大於 50%</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>531</v>
@@ -41805,7 +42641,7 @@
       </c>
       <c r="B52" s="31" t="str">
         <f aca="false">IF(B42&gt;0.5,"強力買進",IF(B42&gt;0.25,"買進",IF(B42&gt;=-0.25,"中立",IF(B42&gt;=-0.5,"放空","強力放空"))))</f>
-        <v>買進</v>
+        <v>強力買進</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>533</v>
@@ -42758,6 +43594,434 @@
       <c r="H140" s="19" t="n">
         <f aca="false">px/E140</f>
         <v>12.0416740548794</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="6" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="4" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="F147" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="G147" s="12" t="s">
+        <v>627</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="J147" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="K147" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="L147" s="12" t="s">
+        <v>632</v>
+      </c>
+      <c r="M147" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="N147" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="O147" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="P147" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="Q147" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="B148" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D148" s="34" t="n">
+        <v>14.892</v>
+      </c>
+      <c r="E148" s="34" t="n">
+        <v>16.601</v>
+      </c>
+      <c r="F148" s="34" t="n">
+        <v>17.4785</v>
+      </c>
+      <c r="G148" s="34" t="n">
+        <v>20.3505</v>
+      </c>
+      <c r="H148" s="34" t="n">
+        <v>23.7165</v>
+      </c>
+      <c r="I148" s="34" t="n">
+        <v>20.0575</v>
+      </c>
+      <c r="J148" s="34" t="n">
+        <v>20.2455</v>
+      </c>
+      <c r="K148" s="34" t="n">
+        <v>22.463</v>
+      </c>
+      <c r="L148" s="34" t="n">
+        <v>20.651</v>
+      </c>
+      <c r="M148" s="34" t="n">
+        <v>20.675</v>
+      </c>
+      <c r="N148" s="8" t="n">
+        <f aca="false">COUNT(D148:M148)</f>
+        <v>10</v>
+      </c>
+      <c r="O148" s="19" t="n">
+        <f aca="false">IF(N148&gt;0,MEDIAN(D148:M148),"")</f>
+        <v>20.298</v>
+      </c>
+      <c r="P148" s="19" t="n">
+        <f aca="false">IF(N148&gt;=7,O148,"")</f>
+        <v>20.298</v>
+      </c>
+      <c r="Q148" s="8" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B149" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D149" s="34" t="n">
+        <v>33.8415</v>
+      </c>
+      <c r="E149" s="34" t="n">
+        <v>36.0395</v>
+      </c>
+      <c r="F149" s="34" t="n">
+        <v>25.549</v>
+      </c>
+      <c r="G149" s="34" t="n">
+        <v>23.381</v>
+      </c>
+      <c r="H149" s="34" t="n">
+        <v>30.371</v>
+      </c>
+      <c r="I149" s="34" t="n">
+        <v>29.6845</v>
+      </c>
+      <c r="J149" s="34" t="n">
+        <v>26.6185</v>
+      </c>
+      <c r="K149" s="34" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="L149" s="34" t="n">
+        <v>42.7395</v>
+      </c>
+      <c r="M149" s="34" t="n">
+        <v>40.689</v>
+      </c>
+      <c r="N149" s="8" t="n">
+        <f aca="false">COUNT(D149:M149)</f>
+        <v>10</v>
+      </c>
+      <c r="O149" s="19" t="n">
+        <f aca="false">IF(N149&gt;0,MEDIAN(D149:M149),"")</f>
+        <v>32.10625</v>
+      </c>
+      <c r="P149" s="19" t="n">
+        <f aca="false">IF(N149&gt;=7,O149,"")</f>
+        <v>32.10625</v>
+      </c>
+      <c r="Q149" s="8" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="0" t="s">
+        <v>492</v>
+      </c>
+      <c r="B150" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D150" s="34" t="n">
+        <v>9.973</v>
+      </c>
+      <c r="E150" s="34" t="n">
+        <v>9.182</v>
+      </c>
+      <c r="F150" s="34" t="n">
+        <v>8.5745</v>
+      </c>
+      <c r="G150" s="34" t="n">
+        <v>9.38</v>
+      </c>
+      <c r="H150" s="34" t="n">
+        <v>7.8455</v>
+      </c>
+      <c r="I150" s="34" t="n">
+        <v>6.496</v>
+      </c>
+      <c r="J150" s="34" t="n">
+        <v>6.4765</v>
+      </c>
+      <c r="K150" s="34" t="n">
+        <v>13.3505</v>
+      </c>
+      <c r="L150" s="34" t="n">
+        <v>23.4305</v>
+      </c>
+      <c r="M150" s="34" t="n">
+        <v>28.9945</v>
+      </c>
+      <c r="N150" s="8" t="n">
+        <f aca="false">COUNT(D150:M150)</f>
+        <v>10</v>
+      </c>
+      <c r="O150" s="19" t="n">
+        <f aca="false">IF(N150&gt;0,MEDIAN(D150:M150),"")</f>
+        <v>9.281</v>
+      </c>
+      <c r="P150" s="19" t="n">
+        <f aca="false">IF(N150&gt;=7,O150,"")</f>
+        <v>9.281</v>
+      </c>
+      <c r="Q150" s="8" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B151" s="0" t="s">
+        <v>496</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="E151" s="34" t="n">
+        <v>10.253</v>
+      </c>
+      <c r="F151" s="34" t="n">
+        <v>11.045</v>
+      </c>
+      <c r="G151" s="34" t="n">
+        <v>15.2965</v>
+      </c>
+      <c r="H151" s="34" t="n">
+        <v>14.1175</v>
+      </c>
+      <c r="I151" s="34" t="n">
+        <v>14.322</v>
+      </c>
+      <c r="J151" s="34" t="n">
+        <v>13.9525</v>
+      </c>
+      <c r="K151" s="34" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="L151" s="34" t="n">
+        <v>13.572</v>
+      </c>
+      <c r="M151" s="34" t="n">
+        <v>12.474</v>
+      </c>
+      <c r="N151" s="8" t="n">
+        <f aca="false">COUNT(D151:M151)</f>
+        <v>9</v>
+      </c>
+      <c r="O151" s="19" t="n">
+        <f aca="false">IF(N151&gt;0,MEDIAN(D151:M151),"")</f>
+        <v>13.9525</v>
+      </c>
+      <c r="P151" s="19" t="n">
+        <f aca="false">IF(N151&gt;=7,O151,"")</f>
+        <v>13.9525</v>
+      </c>
+      <c r="Q151" s="8" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B152" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D152" s="34" t="n">
+        <v>12.7245</v>
+      </c>
+      <c r="E152" s="34" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="F152" s="34" t="n">
+        <v>13.5865</v>
+      </c>
+      <c r="G152" s="34" t="n">
+        <v>13.292</v>
+      </c>
+      <c r="H152" s="34" t="n">
+        <v>11.727</v>
+      </c>
+      <c r="I152" s="34" t="n">
+        <v>10.8985</v>
+      </c>
+      <c r="J152" s="34" t="n">
+        <v>13.589</v>
+      </c>
+      <c r="K152" s="34" t="n">
+        <v>17.484</v>
+      </c>
+      <c r="L152" s="34" t="n">
+        <v>13.758</v>
+      </c>
+      <c r="M152" s="34" t="n">
+        <v>12.6305</v>
+      </c>
+      <c r="N152" s="8" t="n">
+        <f aca="false">COUNT(D152:M152)</f>
+        <v>10</v>
+      </c>
+      <c r="O152" s="19" t="n">
+        <f aca="false">IF(N152&gt;0,MEDIAN(D152:M152),"")</f>
+        <v>13.00825</v>
+      </c>
+      <c r="P152" s="19" t="n">
+        <f aca="false">IF(N152&gt;=7,O152,"")</f>
+        <v>13.00825</v>
+      </c>
+      <c r="Q152" s="8" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="B154" s="19" t="n">
+        <f aca="false">P148</f>
+        <v>20.298</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="B155" s="35" t="n">
+        <f aca="false">COUNT(P149:P152)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B156" s="19" t="n">
+        <f aca="false">IF(B155&gt;0,MEDIAN(P149:P152),"")</f>
+        <v>13.480375</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="B157" s="19" t="n">
+        <f aca="false">IF(AND(ISNUMBER(B154),B155&gt;=2),B154/B156,"")</f>
+        <v>1.50574446185659</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="B158" s="34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E158" s="8" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B159" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" s="8" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B160" s="32" t="n">
+        <f aca="false">IF(ISNUMBER(B157),MIN(MAX(B157,B158),B159),1)</f>
+        <v>1.50574446185659</v>
+      </c>
+      <c r="E160" s="4" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B161" s="25" t="n">
+        <f aca="false">Val!$B$35*B160</f>
+        <v>2960.88891698958</v>
+      </c>
+      <c r="E161" s="4" t="s">
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -42787,7 +44051,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>620</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42795,28 +44059,28 @@
         <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>621</v>
+        <v>661</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>622</v>
+        <v>662</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>623</v>
+        <v>663</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>624</v>
+        <v>664</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>625</v>
+        <v>665</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>626</v>
+        <v>666</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>627</v>
+        <v>667</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>628</v>
+        <v>668</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>350</v>
@@ -42824,12 +44088,12 @@
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>629</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="B5" s="14" t="n">
         <f aca="false">cons_rev26</f>
@@ -42860,15 +44124,15 @@
         <v>-0.0040945569159897</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>631</v>
+        <v>671</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>632</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>633</v>
+        <v>673</v>
       </c>
       <c r="B6" s="14" t="n">
         <f aca="false">cons_eps26</f>
@@ -42899,12 +44163,12 @@
         <v>-0.0032539376779791</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>631</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>634</v>
+        <v>674</v>
       </c>
       <c r="B7" s="14" t="n">
         <f aca="false">cons_rev27</f>
@@ -42935,12 +44199,12 @@
         <v>0.180252032875601</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>631</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>635</v>
+        <v>675</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">cons_eps27</f>
@@ -42971,15 +44235,15 @@
         <v>0.220036035837453</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>631</v>
+        <v>671</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>636</v>
+        <v>676</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>637</v>
+        <v>677</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">cons_eps28</f>
@@ -43010,17 +44274,17 @@
         <v>-0.438700061033887</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>631</v>
+        <v>671</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>638</v>
+        <v>678</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>639</v>
+        <v>679</v>
       </c>
       <c r="B11" s="18" t="n">
         <f aca="false">br_sw26</f>
@@ -43051,15 +44315,15 @@
         <v>5.03066014999054E-005</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>640</v>
+        <v>680</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>641</v>
+        <v>681</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>642</v>
+        <v>682</v>
       </c>
       <c r="B12" s="18" t="n">
         <f aca="false">1-dell_top2</f>
@@ -43090,15 +44354,15 @@
         <v>-0.315243207848114</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>643</v>
+        <v>683</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>644</v>
+        <v>684</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>645</v>
+        <v>685</v>
       </c>
       <c r="C13" s="18" t="n">
         <f aca="false">PL!E91</f>
@@ -43118,7 +44382,7 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>646</v>
+        <v>686</v>
       </c>
       <c r="C14" s="15" t="n">
         <f aca="false">(PL!E76+PL!E81)/fx/itc_27</f>
@@ -43133,12 +44397,12 @@
         <v>0.0120349516524039</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>647</v>
+        <v>687</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
-        <v>648</v>
+        <v>688</v>
       </c>
       <c r="C15" s="19" t="n">
         <f aca="false">PL!D79/fx</f>
@@ -43156,17 +44420,17 @@
         <v>112</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>649</v>
+        <v>689</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>650</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>651</v>
+        <v>691</v>
       </c>
       <c r="C17" s="18" t="n">
         <f aca="false">PL!D94</f>
@@ -43181,15 +44445,15 @@
         <v>0.219589247962076</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>652</v>
+        <v>692</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>653</v>
+        <v>693</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="0" t="s">
-        <v>654</v>
+        <v>694</v>
       </c>
       <c r="B18" s="18" t="n">
         <f aca="false">a26_gp/a26_rev</f>
@@ -43220,7 +44484,7 @@
         <v>0.00870179920326036</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>655</v>
+        <v>695</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43255,20 +44519,20 @@
         <v>0.0480733260882966</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>656</v>
+        <v>696</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>657</v>
+        <v>697</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
-        <v>658</v>
+        <v>698</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>659</v>
+        <v>699</v>
       </c>
     </row>
   </sheetData>
@@ -43297,53 +44561,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>660</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>661</v>
+        <v>701</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>662</v>
+        <v>702</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>663</v>
+        <v>703</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>664</v>
+        <v>704</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>665</v>
+        <v>705</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>566</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>666</v>
+        <v>706</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>667</v>
+        <v>707</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>668</v>
+        <v>708</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>669</v>
+        <v>709</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>670</v>
+        <v>710</v>
       </c>
       <c r="L3" s="12" t="s">
-        <v>671</v>
+        <v>711</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>672</v>
+        <v>712</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>673</v>
+        <v>713</v>
       </c>
       <c r="C4" s="20" t="n">
         <f aca="false">PL!E84</f>
@@ -43388,10 +44652,10 @@
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>674</v>
+        <v>714</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>675</v>
+        <v>715</v>
       </c>
       <c r="C5" s="20" t="n">
         <f aca="false">E64</f>
@@ -43436,10 +44700,10 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>676</v>
+        <v>716</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>677</v>
+        <v>717</v>
       </c>
       <c r="C6" s="20" t="n">
         <f aca="false">E112</f>
@@ -43484,10 +44748,10 @@
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>678</v>
+        <v>718</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>679</v>
+        <v>719</v>
       </c>
       <c r="C7" s="20" t="n">
         <f aca="false">E160</f>
@@ -43532,10 +44796,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>680</v>
+        <v>720</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>681</v>
+        <v>721</v>
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">E208</f>
@@ -43580,10 +44844,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>682</v>
+        <v>722</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>683</v>
+        <v>723</v>
       </c>
       <c r="C9" s="20" t="n">
         <f aca="false">E256</f>
@@ -43628,10 +44892,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>685</v>
+        <v>725</v>
       </c>
       <c r="C10" s="20" t="n">
         <f aca="false">E304</f>
@@ -43676,10 +44940,10 @@
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>686</v>
+        <v>726</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>687</v>
+        <v>727</v>
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">E352</f>
@@ -43724,10 +44988,10 @@
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>688</v>
+        <v>728</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>689</v>
+        <v>729</v>
       </c>
       <c r="C12" s="20" t="n">
         <f aca="false">E400</f>
@@ -43772,10 +45036,10 @@
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>690</v>
+        <v>730</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>691</v>
+        <v>731</v>
       </c>
       <c r="C13" s="20" t="n">
         <f aca="false">E448</f>
@@ -43820,10 +45084,10 @@
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>692</v>
+        <v>732</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>693</v>
+        <v>733</v>
       </c>
       <c r="C14" s="20" t="n">
         <f aca="false">E496</f>
@@ -43868,10 +45132,10 @@
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>694</v>
+        <v>734</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>695</v>
+        <v>735</v>
       </c>
       <c r="C15" s="20" t="n">
         <f aca="false">E544</f>
@@ -43916,10 +45180,10 @@
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>696</v>
+        <v>736</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>697</v>
+        <v>737</v>
       </c>
       <c r="C16" s="20" t="n">
         <f aca="false">E592</f>
@@ -43964,10 +45228,10 @@
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>698</v>
+        <v>738</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>699</v>
+        <v>739</v>
       </c>
       <c r="C17" s="20" t="n">
         <f aca="false">E640</f>
@@ -44012,10 +45276,10 @@
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>700</v>
+        <v>740</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>701</v>
+        <v>741</v>
       </c>
       <c r="C18" s="20" t="n">
         <f aca="false">E688</f>
@@ -44060,10 +45324,10 @@
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>702</v>
+        <v>742</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>703</v>
+        <v>743</v>
       </c>
       <c r="C19" s="20" t="n">
         <f aca="false">E736</f>
@@ -44108,10 +45372,10 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>704</v>
+        <v>744</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>705</v>
+        <v>745</v>
       </c>
       <c r="C20" s="20" t="n">
         <f aca="false">E784</f>
@@ -44156,10 +45420,10 @@
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>706</v>
+        <v>746</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>707</v>
+        <v>747</v>
       </c>
       <c r="C21" s="20" t="n">
         <f aca="false">PL!E132</f>
@@ -44204,10 +45468,10 @@
     </row>
     <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>708</v>
+        <v>748</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>709</v>
+        <v>749</v>
       </c>
       <c r="C22" s="20" t="n">
         <f aca="false">PL!E180</f>
@@ -44252,124 +45516,124 @@
     </row>
     <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
-        <v>710</v>
+        <v>750</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>711</v>
+        <v>751</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>712</v>
+        <v>752</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>713</v>
+        <v>753</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>714</v>
+        <v>754</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>715</v>
+        <v>755</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>716</v>
+        <v>756</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>717</v>
+        <v>757</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>718</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>719</v>
+        <v>759</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>720</v>
+        <v>760</v>
       </c>
       <c r="C28" s="28" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12)))*(1+(tp_r-0.01))+(1-tp_w_dcf)*Val!$B$35</f>
-        <v>2522.26187343976</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r-0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r-0.01)-tp_g)/(1+(tp_r-0.01))^Val!$F$12)))*(1+(tp_r-0.01))+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>3019.50865397703</v>
       </c>
       <c r="D28" s="18" t="n">
         <f aca="false">C28/G28-1</f>
-        <v>0.10866717001802</v>
+        <v>0.0891762552136743</v>
       </c>
       <c r="E28" s="28" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12)))*(1+(tp_r+0.01))+(1-tp_w_dcf)*Val!$B$35</f>
-        <v>2098.47751358077</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+(tp_r+0.01))^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/((tp_r+0.01)-tp_g)/(1+(tp_r+0.01))^Val!$F$12)))*(1+(tp_r+0.01))+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>2595.72429411804</v>
       </c>
       <c r="F28" s="18" t="n">
         <f aca="false">E28/G28-1</f>
-        <v>-0.0776084153564763</v>
+        <v>-0.0636883048800323</v>
       </c>
       <c r="G28" s="28" t="n">
         <f aca="false">Val!$B$39</f>
-        <v>2275.03974290026</v>
+        <v>2772.28652343754</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>721</v>
+        <v>761</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>722</v>
+        <v>762</v>
       </c>
       <c r="C29" s="28" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*Val!$B$35</f>
-        <v>2162.12814507803</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g-0.01)/tp_roe))*(1+(tp_g-0.01))/(tp_r-(tp_g-0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>2659.3749256153</v>
       </c>
       <c r="D29" s="18" t="n">
         <f aca="false">C29/G29-1</f>
-        <v>-0.0496306045529977</v>
+        <v>-0.0407286897900545</v>
       </c>
       <c r="E29" s="28" t="n">
-        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*Val!$B$35</f>
-        <v>2436.09802541398</v>
+        <f aca="false">tp_w_dcf*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,(tp_g+0.01)/tp_roe))*(1+(tp_g+0.01))/(tp_r-(tp_g+0.01))/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-tp_w_dcf)*tp_comp_adj</f>
+        <v>2933.34480595125</v>
       </c>
       <c r="F29" s="18" t="n">
         <f aca="false">E29/G29-1</f>
-        <v>0.0707936127341635</v>
+        <v>0.0580958285343487</v>
       </c>
       <c r="G29" s="28" t="n">
         <f aca="false">Val!$B$39</f>
-        <v>2275.03974290026</v>
+        <v>2772.28652343754</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>723</v>
+        <v>763</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>724</v>
+        <v>764</v>
       </c>
       <c r="C30" s="28" t="n">
-        <f aca="false">0.3*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.3)*Val!$B$35</f>
-        <v>2151.58198810617</v>
+        <f aca="false">0.3*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.3)*tp_comp_adj</f>
+        <v>2847.72748085836</v>
       </c>
       <c r="D30" s="18" t="n">
         <f aca="false">C30/G30-1</f>
-        <v>-0.05426619696617</v>
+        <v>0.027212539823364</v>
       </c>
       <c r="E30" s="28" t="n">
-        <f aca="false">0.7*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.7)*Val!$B$35</f>
-        <v>2398.49749769435</v>
+        <f aca="false">0.7*(tp_wA*(MAX(0,Val!B7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!B8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!B9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!B10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!B11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!B12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!B12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wB*(MAX(0,Val!C7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!C8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!C9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!C10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!C11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!C12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!C12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12))+tp_wC*(MAX(0,Val!D7*Val!$G$7*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$7+Val!D8*Val!$G$8*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$8+Val!D9*Val!$G$9*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$9+Val!D10*Val!$G$10*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$10+Val!D11*Val!$G$11*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$11+Val!D12*Val!$G$12*(1-MIN(0.8,tp_g/tp_roe))/(1+tp_r)^Val!$F$12+Val!D12*(1-MIN(0.8,tp_g/tp_roe))*(1+tp_g)/(tp_r-tp_g)/(1+tp_r)^Val!$F$12)))*(1+tp_r)+(1-0.7)*tp_comp_adj</f>
+        <v>2696.84556601672</v>
       </c>
       <c r="F30" s="18" t="n">
         <f aca="false">E30/G30-1</f>
-        <v>0.0542661969661695</v>
+        <v>-0.0272125398233639</v>
       </c>
       <c r="G30" s="28" t="n">
         <f aca="false">Val!$B$39</f>
-        <v>2275.03974290026</v>
+        <v>2772.28652343754</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>725</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45390,7 +46654,7 @@
     </row>
     <row r="88" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>726</v>
+        <v>766</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -46411,7 +47675,7 @@
     </row>
     <row r="136" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>727</v>
+        <v>767</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -47432,7 +48696,7 @@
     </row>
     <row r="184" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>728</v>
+        <v>768</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48453,7 +49717,7 @@
     </row>
     <row r="232" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="1" t="s">
-        <v>729</v>
+        <v>769</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49474,7 +50738,7 @@
     </row>
     <row r="280" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="1" t="s">
-        <v>730</v>
+        <v>770</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -50495,7 +51759,7 @@
     </row>
     <row r="328" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="1" t="s">
-        <v>731</v>
+        <v>771</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -51516,7 +52780,7 @@
     </row>
     <row r="376" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="1" t="s">
-        <v>732</v>
+        <v>772</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52537,7 +53801,7 @@
     </row>
     <row r="424" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="1" t="s">
-        <v>733</v>
+        <v>773</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -53558,7 +54822,7 @@
     </row>
     <row r="472" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="1" t="s">
-        <v>734</v>
+        <v>774</v>
       </c>
     </row>
     <row r="473" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -54579,7 +55843,7 @@
     </row>
     <row r="520" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="1" t="s">
-        <v>735</v>
+        <v>775</v>
       </c>
     </row>
     <row r="521" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -55600,7 +56864,7 @@
     </row>
     <row r="568" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="1" t="s">
-        <v>736</v>
+        <v>776</v>
       </c>
     </row>
     <row r="569" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56621,7 +57885,7 @@
     </row>
     <row r="616" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="1" t="s">
-        <v>737</v>
+        <v>777</v>
       </c>
     </row>
     <row r="617" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57642,7 +58906,7 @@
     </row>
     <row r="664" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="s">
-        <v>738</v>
+        <v>778</v>
       </c>
     </row>
     <row r="665" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -58663,7 +59927,7 @@
     </row>
     <row r="712" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A712" s="1" t="s">
-        <v>739</v>
+        <v>779</v>
       </c>
     </row>
     <row r="713" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -59684,7 +60948,7 @@
     </row>
     <row r="760" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A760" s="1" t="s">
-        <v>740</v>
+        <v>780</v>
       </c>
     </row>
     <row r="761" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -60728,172 +61992,172 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>741</v>
+        <v>781</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>743</v>
+        <v>783</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>744</v>
+        <v>784</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>745</v>
+        <v>785</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>746</v>
+        <v>786</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>747</v>
+        <v>787</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>748</v>
+        <v>788</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>749</v>
+        <v>789</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>750</v>
+        <v>790</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>751</v>
+        <v>791</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>753</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>754</v>
+        <v>794</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>755</v>
+        <v>795</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>757</v>
+        <v>797</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>758</v>
+        <v>798</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>759</v>
+        <v>799</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>760</v>
+        <v>800</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>761</v>
+        <v>801</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>762</v>
+        <v>802</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>763</v>
+        <v>803</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>764</v>
+        <v>804</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>765</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>766</v>
+        <v>806</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>767</v>
+        <v>807</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>768</v>
+        <v>808</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>769</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>770</v>
+        <v>810</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>771</v>
+        <v>811</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>772</v>
+        <v>812</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>773</v>
+        <v>813</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>774</v>
+        <v>814</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>775</v>
+        <v>815</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>776</v>
+        <v>816</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>777</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>778</v>
+        <v>818</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>779</v>
+        <v>819</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>780</v>
+        <v>820</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
-        <v>781</v>
+        <v>821</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>782</v>
+        <v>822</v>
       </c>
     </row>
   </sheetData>
